--- a/output/pdf_financials_xlsx/EMR.xlsx
+++ b/output/pdf_financials_xlsx/EMR.xlsx
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>11.893992</v>
+        <v>0.221734</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10.034848</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.771992</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-2.146174</v>
@@ -1360,16 +1360,16 @@
         <v>-4.67612</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.375731</v>
+        <v>-0.375731</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.474953</v>
+        <v>-0.474953</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.272193</v>
@@ -1390,10 +1390,10 @@
         <v>-0.720676</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.570883</v>
+        <v>-1.570883</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>-0.546299</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.836129</v>
+        <v>-5.836129</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.017424</v>
+        <v>-5.017424</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.385996</v>
+        <v>-2.385996</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.073087</v>
@@ -1692,16 +1692,16 @@
         <v>-2.33806</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.375731</v>
+        <v>-0.375731</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.474953</v>
+        <v>-0.474953</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.272193</v>
@@ -1722,10 +1722,10 @@
         <v>-0.720676</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.570883</v>
+        <v>-1.570883</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>-0.546299</v>
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.836129</v>
+        <v>-5.836129</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.017424</v>
+        <v>-5.017424</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.385996</v>
+        <v>-2.385996</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.073087</v>
@@ -1884,16 +1884,16 @@
         <v>-2.33806</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.375731</v>
+        <v>-0.375731</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.474953</v>
+        <v>-0.474953</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.272193</v>
@@ -1914,10 +1914,10 @@
         <v>-0.720676</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.570883</v>
+        <v>-1.570883</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>-0.546299</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10.238823</v>
+        <v>-10.238823</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>15.67945</v>
+        <v>-15.67945</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>17.042829</v>
+        <v>-17.042829</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>21.46174</v>
@@ -2122,10 +2122,10 @@
         <v>12.011267</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-17.454256</v>
+        <v>17.454256</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-27.5417</v>
+        <v>27.5417</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>27.31495</v>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>11.893992</v>
+        <v>0.221734</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>10.034848</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.771992</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.146174</v>
@@ -2158,16 +2158,16 @@
         <v>-4.67612</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.375731</v>
+        <v>-0.375731</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.474953</v>
+        <v>-0.474953</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.272193</v>
@@ -2188,10 +2188,10 @@
         <v>-0.720676</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.570883</v>
+        <v>-1.570883</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>-0.546299</v>
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>11.893992</v>
+        <v>0.221734</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.034848</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.771992</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.13196</v>
@@ -2286,16 +2286,16 @@
         <v>-4.661642</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.375731</v>
+        <v>-0.375731</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.474953</v>
+        <v>-0.474953</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.272193</v>
@@ -2316,10 +2316,10 @@
         <v>-0.720676</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.570883</v>
+        <v>-1.570883</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>-0.546299</v>
@@ -2437,13 +2437,17 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>50.93212606835451</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>50</v>
+        <v>2732.040643293315</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="3" t="n">
         <v>-50</v>
@@ -2452,16 +2456,16 @@
         <v>-50</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -2482,10 +2486,10 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>-0</v>
@@ -6962,25 +6966,25 @@
         <v>6.800722</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.686349</v>
+        <v>7.74913</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.686349</v>
+        <v>7.74913</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.686349</v>
+        <v>7.74913</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.686349</v>
+        <v>7.74913</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.686349</v>
+        <v>7.74913</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.701802</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.803764</v>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
@@ -6996,13 +7000,13 @@
         <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.026749</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>1.071598</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>1.589337</v>
       </c>
     </row>
     <row r="93">
@@ -11638,7 +11642,11 @@
           <t>Warrant reserve (note 16)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -13259,7 +13267,11 @@
           <t>Warrant reserve (note 13)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -17037,7 +17049,11 @@
           <t>Warrants - reserve 11</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -66891,10 +66907,10 @@
         </is>
       </c>
       <c r="U520" s="5" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="V520" s="5" t="n">
-        <v>0.546299</v>
+        <v>-0.546299</v>
       </c>
       <c r="W520" t="inlineStr">
         <is>
@@ -68545,10 +68561,10 @@
         </is>
       </c>
       <c r="T535" s="5" t="n">
-        <v>1.570883</v>
+        <v>-1.570883</v>
       </c>
       <c r="U535" s="5" t="n">
-        <v>0.826251</v>
+        <v>-0.826251</v>
       </c>
       <c r="V535" t="inlineStr">
         <is>
@@ -84914,13 +84930,13 @@
         </is>
       </c>
       <c r="L684" s="5" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="M684" s="5" t="n">
-        <v>0.474953</v>
+        <v>-0.474953</v>
       </c>
       <c r="N684" s="5" t="n">
-        <v>0.272193</v>
+        <v>-0.272193</v>
       </c>
       <c r="O684" t="inlineStr">
         <is>
@@ -87880,10 +87896,10 @@
         </is>
       </c>
       <c r="K711" s="5" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="L711" s="5" t="n">
-        <v>0.244138</v>
+        <v>-0.244138</v>
       </c>
       <c r="M711" t="inlineStr">
         <is>
@@ -89312,10 +89328,10 @@
         </is>
       </c>
       <c r="J724" s="5" t="n">
-        <v>0.375731</v>
+        <v>-0.375731</v>
       </c>
       <c r="K724" s="5" t="n">
-        <v>0.258169</v>
+        <v>-0.258169</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -95402,16 +95418,16 @@
         </is>
       </c>
       <c r="E779" s="5" t="n">
-        <v>5.836129</v>
+        <v>-5.836129</v>
       </c>
       <c r="F779" s="5" t="n">
-        <v>5.017424</v>
+        <v>-5.017424</v>
       </c>
       <c r="G779" s="5" t="n">
-        <v>2.385996</v>
+        <v>-2.385996</v>
       </c>
       <c r="H779" s="5" t="n">
-        <v>1.080206</v>
+        <v>-1.080206</v>
       </c>
       <c r="I779" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EMR.xlsx
+++ b/output/pdf_financials_xlsx/EMR.xlsx
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.08631</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.063537</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001537</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000261</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.012303</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2143,16 +2143,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.221734</v>
+        <v>0.308044</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>0.063537</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
+        <v>0.001537</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.146174</v>
+        <v>-2.145913</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-4.67612</v>
@@ -2185,7 +2185,7 @@
         <v>-0.357837</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.720676</v>
+        <v>-0.732979</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-1.570883</v>
@@ -2271,16 +2271,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.221734</v>
+        <v>0.308044</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>0.063537</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>0.001537</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.13196</v>
+        <v>-2.131699</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-4.661642</v>
@@ -2313,7 +2313,7 @@
         <v>-0.357837</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.720676</v>
+        <v>-0.732979</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-1.570883</v>
@@ -2649,10 +2649,10 @@
         <v>0.018572</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.203042</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.160361</v>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
         <v>0.018572</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>2.061648</v>
+        <v>2.26469</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.516168</v>
+        <v>0.676529</v>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
@@ -3673,10 +3673,10 @@
         <v>0.163445</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.366755</v>
+        <v>0.163713</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.339783</v>
+        <v>0.179422</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -9035,16 +9035,16 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005365</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005844</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.006378</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.00696</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -9074,16 +9074,16 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004569</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010888</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018245</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018093</v>
       </c>
       <c r="S124" s="3" t="n">
         <v>0</v>
@@ -9099,16 +9099,16 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005365</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005844</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.006378</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.00696</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -9138,16 +9138,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004569</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010888</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018245</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018093</v>
       </c>
       <c r="S125" s="3" t="n">
         <v>0</v>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -34852,7 +34852,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -43037,7 +43041,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -55989,7 +55997,11 @@
           <t>Purchase of reclamation deposit</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -58397,7 +58409,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -59941,7 +59957,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -61338,7 +61358,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E469" s="5" t="n">
         <v>-0.005365</v>
       </c>
@@ -69534,7 +69558,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -92540,7 +92564,7 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -95303,7 +95327,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -97794,7 +97818,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E801" s="5" t="n">

--- a/output/pdf_financials_xlsx/EMR.xlsx
+++ b/output/pdf_financials_xlsx/EMR.xlsx
@@ -2243,25 +2243,25 @@
         <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.003148</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.019611</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.025749</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.01468</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.023659</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.007539</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0</v>
+        <v>0.006004</v>
       </c>
     </row>
     <row r="29">
@@ -2307,25 +2307,25 @@
         <v>-2.506911</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.506911</v>
+        <v>-2.503763</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.357837</v>
+        <v>-0.338226</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.732979</v>
+        <v>-0.70723</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.570883</v>
+        <v>-1.556203</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.826251</v>
+        <v>-0.802592</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.546299</v>
+        <v>-0.53876</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>0.275532</v>
+        <v>0.281536</v>
       </c>
     </row>
     <row r="30">
@@ -7529,19 +7529,19 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.003148</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.019611</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.025749</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.01468</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.014188</v>
       </c>
       <c r="S100" s="3" t="n">
         <v>0</v>
@@ -33859,7 +33859,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -35732,7 +35736,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -38049,7 +38057,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -44369,7 +44381,11 @@
           <t>Depreciation of right-of-use assets 14</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -45471,7 +45487,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -62681,7 +62701,11 @@
           <t>Amortization of tangible assets (note 10)</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -65963,7 +65987,11 @@
           <t>Amortization of tangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -66072,7 +66100,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -67400,7 +67432,11 @@
           <t>Depreciation of right of use asset 11)</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
@@ -69146,7 +69182,11 @@
           <t>Depreciation of right-of-use asset 13</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -75857,7 +75897,11 @@
           <t>Depreciation of right-of-use asset 14</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
           <t>-</t>
